--- a/下载追踪表.xlsx
+++ b/下载追踪表.xlsx
@@ -426,25 +426,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="45" customWidth="1" min="17" max="17"/>
+    <col width="25" customWidth="1" min="18" max="18"/>
+    <col width="45" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
+    <col width="45" customWidth="1" min="21" max="21"/>
+    <col width="45" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,59 +486,201 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>讲师</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>选课链接</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>回放链接</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>文稿链接</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>作业链接</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>作业飞书</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Candy1标题</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Candy1链接</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Candy2标题</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Candy2链接</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Candy3标题</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Candy3链接</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Candy4标题</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Candy4链接</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>其他链接</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>视频下载</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>音频提取</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>文稿下载</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>音频转录</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>整体状态</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>文件路径</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>失败原因</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>创业必修</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>商业预判</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>全员必修：重新理解「机会预判」</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>周子敬</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/nLQ05cf204a4e7b8?tab=content</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://air.yitang.top/live/iQxL0D3WZi?lessonId=nLQ05cf204a4e7b8&amp;noTrial=1&amp;_uds=pd_lesson_detail_air&amp;ticket=LvOMJ08nefW83EwY&amp;u=635801</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://yitang.top/fs-doc/nLQ05cf204a4e7b8/Xl5BdoiOlokDhnxolnmchp6Dnpd?fromAcl=lesson-founder</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://yitang.top/homework/nLQ05cf204a4e7b8/view</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://ycnvlssgqsaj.feishu.cn/wiki/XiHewccLyiIaLjkk74pcD0jFnie?from=from_copylink</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>预判踩坑数据包</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://yitang.top/fs-doc/nLQ05cf204a4e7b8/K4FrdInYMo0VMixxAaccSCiFngf?fromAcl=lesson-founder</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>优秀提示词合集</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>https://yitang.top/fs-doc/nLQ05cf204a4e7b8/Cr3Pdqn1FobCnOxE8xac9bNdnAe?fromAcl=lesson-founder</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/下载追踪表.xlsx
+++ b/下载追踪表.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -599,7 +599,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>创业必修</t>
@@ -665,22 +664,58 @@
           <t>https://yitang.top/fs-doc/nLQ05cf204a4e7b8/Cr3Pdqn1FobCnOxE8xac9bNdnAe?fromAcl=lesson-founder</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>行业画布：行业机会预判必修课</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>周子敬</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/L3np5cf204fb0260</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>无链接</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/下载追踪表.xlsx
+++ b/下载追踪表.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:AC127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -674,9 +674,6 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>行业画布：行业机会预判必修课</t>
@@ -692,30 +689,6947 @@
           <t>https://yitang.top/lesson/L3np5cf204fb0260</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
           <t>无链接</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>商业大航海 - 专家分享｜我如何把一堂课，变成一个 AI 工具（半肥猫）</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>半肥猫（紫鲸 AI 创始人）</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/商业大航海/商业大航海-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>图片数: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>清单体笔记</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/清单体笔记/清单体笔记-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>图片数: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>兰毅-产品思维做组织</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/兰毅-产品思维做组织/兰毅-产品思维做组织-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>图片数: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>科学成长体系</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/科学成长体系/科学成长体系-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>图片数: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Truman-建模与追求</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/Truman-建模与追求/Truman-建模与追求-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>图片数: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI 2041：预见未来二十年</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/AI2041/AI2041-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>图片数: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>晓莉-转化率</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/晓莉-转化率/晓莉-转化率-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>图片数: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>讲香实操：一堂十指模型</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/xOXP66e39bc5b2e1?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/卖点讲香/讲香实操 一堂十指模型-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>全员必修：深度复盘第一课</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/sdD1659d331c0d74?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/深度复盘/全员必修 深度复盘第一课-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>一堂笔记法：清单式解题练习</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/8BwK673dae60bcc2?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/练记笔记/一堂笔记法 清单式解题练习-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>全员必修：时间管理必修课</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/weh4666032172e68?_uds=fwh_lesson_map&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/时间管理/全员必修 时间管理必修课-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>全员必修：重新理解「人工智能」</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/5PzM64d5aee72613?_uds=fwh_lesson_map&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/AI力/全员必修 重新理解「人工智能」-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>人工智能入门：提示词必修课</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>于陆</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/7hFn66456b279514?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/AI力/人工智能入门 提示词必修课-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>全员必修：AI场景第一课</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/D24Q690b18f8d450?_uds=latest-courses&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/AI力/全员必修 AI场景第一课-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>全员必修：AI上手第一课</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/jpgT68f8af98ec8b?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/AI力/全员必修 AI上手第一课-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>刻意练习：重新理解「科学成长」</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/7LTx64019aea3dae?tab=content</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/刻意练习/刻意练习 重新理解「科学成长」-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>表达力1：科学表达必修课</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/kyoz63ea596bca9f?_uds=homepage_lesson_search&amp;searchSessionId=ff2c41f000eb8c5f</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/表达力/表达力1 科学表达必修课-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>图片数: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>全员必修：知识管理必修课</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/hvcX647ec8413892?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/知识管理/全员必修 知识管理必修课-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>全员必修：灵感闪现认知篇</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/ldeb68a577cf99d8?_uds=homepage</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/灵感闪现/全员必修 灵感闪现认知篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>红点实操2：路径规划篇</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/OCam66fa279c865c?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/人生红点/红点实操2 路径规划篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>全员必修：人生红点认知篇</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/Hr_f655f23747552?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/人生红点/全员必修 人生红点认知篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>红点实操1：笃定红点篇</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/jUIG66ec197ae86b?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/人生红点/红点实操1 笃定红点篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>IPO实操篇：IPO落地武器库</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/0UGd67b581fd308c?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/科学学习/IPO实操篇 IPO落地武器库-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>IPO认知篇：重新理解「科学学习」</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/dQfx5d4803dc3f91?_uds=null</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/科学学习/IPO认知篇 重新理解「科学学习」-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>写逐字稿</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/个人必修/写逐字稿/写逐字稿-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>图片数: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>增长实操：渠道探索必修课</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/wWED6760e3049cd0?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/渠道探索/增长实操 渠道探索必修课/增长实操 渠道探索必修课-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>需求实操1：剥离拆解篇</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/7etN6939409aa0a8?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/需求分析/需求实操1 剥离拆解篇/需求实操1 剥离拆解篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>需求实操4：算天花板篇</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/6eT669d60cf89b5c?_uds=latest-courses&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/需求分析/需求实操4 算天花板篇/需求实操4 算天花板篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>需求实操2：场景推演篇</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/uDcE69672ff34b0f?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/需求分析/需求实操2 场景推演篇/需求实操2 场景推演篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>需求实操3：定性评估篇</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/dKPk6979e7e5510e?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/需求分析/需求实操3 定性评估篇/需求实操3 定性评估篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>产品内核3：找到精准内核</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/FGmt6596c5e46c25?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/产品内核/产品内核3 找到精准内核/产品内核3 找到精准内核-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>产品内核4：动态迭代内核</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/9HJk65faa9454056?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/产品内核/产品内核4 动态迭代内核/产品内核4 动态迭代内核-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>产品内核2：剥离最小内核</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/UdJQ65780f56e987?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/产品内核/产品内核2 剥离最小内核/产品内核2 剥离最小内核-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>科学做事：商务送礼必修课</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/oXZe65bc55db59e0?_uds=fwh_lesson_map&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/科学送礼/科学做事 商务送礼必修课/科学做事 商务送礼必修课-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>图片数: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>单元模型5：动态预测模型</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/Xfq061d489903272?tab=content</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/单元模型/单元模型5 动态预测模型/单元模型5 动态预测模型-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>单元模型3：构建完整模型</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/4KQD6178fc079b78?tab=content</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/单元模型/单元模型3 构建完整模型/单元模型3 构建完整模型-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>图片数: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>单元模型2：选择核心模型</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/aNuT615499b97426?tab=content</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/单元模型/单元模型2 选择核心模型/单元模型2 选择核心模型-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>单元模型4：找准基准值</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>你这个事情不适合融资啊，投资人不看的，你知道能做大上市的Benchmark是多少么？*</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/R3pP61c17092ef24?tab=content</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/单元模型/单元模型4 找准基准值/单元模型4 找准基准值-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>全员必修：重新理解「科学理念」</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/dkCl6568649d9fa1?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/科学理念/全员必修 重新理解「科学理念」/全员必修 重新理解「科学理念」-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>低成本验证实操1：剥离假设篇</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/UFpS5e12eb5f8193?tab=content</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/精益实验/低成本验证实操1 剥离假设篇/低成本验证实操1 剥离假设篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>全员必修：低成本验证认知篇</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/tqAr5ebe66e85694?tab=content</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/精益实验/全员必修 低成本验证认知篇/全员必修 低成本验证认知篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>低成本验证实操2：MVP设计篇</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/bITV5e12eb693b74?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/精益实验/低成本验证实操2 MVP设计篇/低成本验证实操2 MVP设计篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>低成本验证实操3：系统测试篇</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/Bl4F68244fdd601e?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/精益实验/低成本验证实操3 系统测试篇/低成本验证实操3 系统测试篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>调研黑客：系统式调研实操篇</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/5ElX69fb477eb20d?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/情报调研/调研黑客 系统式调研实操篇/调研黑客 系统式调研实操篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>图片数: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>调研黑客：挖掘式调研武器库</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/JUiv5e8c5f07432b?tab=content</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/情报调研/调研黑客 挖掘式调研武器库/调研黑客 挖掘式调研武器库-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>全员必修：重新理解「情报调研」</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/b1I66377680b3b4e?_uds=null</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/情报调研/全员必修 重新理解「情报调研」/全员必修 重新理解「情报调研」-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>调研专项：高质量的专家访谈</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/1_Z460e53cca4b54?tab=content</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/情报调研/调研专项 高质量的专家访谈/调研专项 高质量的专家访谈-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>调研黑客：系统式调研认知篇</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>张磊</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/sauD5e8c5eee00d9?tab=content</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/情报调研/调研黑客 系统式调研认知篇/调研黑客 系统式调研认知篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>预判实操1：预判商业篇</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/ZsHV695e2c23c419?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/商业预判/预判实操1 预判商业篇/预判实操1 预判商业篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>全员必修：重新理解「机会预判」</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>周子敬</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/nLQ05cf204a4e7b8?tab=content</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/商业预判/全员必修 重新理解「机会预判」/全员必修 重新理解「机会预判」-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>增长实操：工业化生产必修课</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/wRQb677e7c73c534?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/建工业化/增长实操 工业化生产必修课/增长实操 工业化生产必修课-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>全员必修：重新理解「解放思想」</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/m6WS6528d19c80b1?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/解放思想/全员必修 重新理解「解放思想」/全员必修 重新理解「解放思想」-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>全员必修：重新理解「关键假设」</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/A_Iz6571617cf3dc?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/关键假设/全员必修 重新理解「关键假设」/全员必修 重新理解「关键假设」-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>全员必修：一堂五步法落地篇</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/oQRa6774ba3de7f5?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/关键假设/全员必修 一堂五步法落地篇/全员必修 一堂五步法落地篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>五步法进阶1：重新理解「需求原点」</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/Gf4R6065c9d7dda8?tab=content</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/关键假设/五步法进阶1 重新理解「需求原点」/五步法进阶1 重新理解「需求原点」-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>领域专项：一堂五步法企业服务篇</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>徐剑</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/tVJX63df3aa37a42?tab=content</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/关键假设/领域专项 一堂五步法企业服务篇/领域专项 一堂五步法企业服务篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>全员必修：重新理解「一堂五步法」</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/UMDo63e5dd17b615?_uds=null</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/关键假设/全员必修 重新理解「一堂五步法」/全员必修 重新理解「一堂五步法」-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>五步法进阶2：重新理解「解决方案」</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/4zjx605d6eaa7c5c?tab=content</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/关键假设/五步法进阶2 重新理解「解决方案」 (产品内核1)/五步法进阶2 重新理解「解决方案」 (产品内核1)-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>五步法进阶3：重新理解「商业模式」</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/jVaJ60af62f56d7f?_uds=homepage</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/关键假设/五步法进阶3 重新理解「商业模式」 (单元模型1)/五步法进阶3 重新理解「商业模式」 (单元模型1)-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>图片数: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>五步法进阶4：重新理解「业务增长」</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/yqdc610ebc20d7f9?tab=content</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/关键假设/五步法进阶4 重新理解「业务增长」/五步法进阶4 重新理解「业务增长」-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>全员必修：重新理解「业务里程碑」</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/1qeQ5d480428290a?tab=content</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/文稿/创业必修/关键假设/全员必修 重新理解「业务里程碑」/全员必修 重新理解「业务里程碑」-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>十倍成长：刻意练习×AI开源专场</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/OZXa6746e0273ae1?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/练习高手/十倍成长 刻意练习×AI开源专场-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>十倍成长：3个刻意练习最佳实践</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>兰军</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/R6U1641189134676?_uds=null&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/练习高手/十倍成长 3个刻意练习最佳实践-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AI案例：冠成的AI落地最佳实践</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>冠成</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/lXN_6914618d636c?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/AI落地高手/AI案例 冠成的AI落地最佳实践-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>聪明精益：张磊的3个业务实验</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>张磊</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/5WdV5f34d2d94267?_uds=null&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/精益高手/聪明精益 张磊的3个业务实验-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>团队成长：4个苦练基本功实践</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>白忱</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/IwfB650d0b02886f?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/实践高手/团队成长 4个苦练基本功实践-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>探索高手：3个视频号最佳实践复盘</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vikki</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/jflv682d80022948?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/短视频高手/探索高手 3个视频号最佳实践复盘-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>知识管理开源：小红书、医疗和个人</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>**今天是我在一堂的第3次讲课，之前讲过一节4个半小时的连锁门店业务完整的案例复盘大课，还作为22界学员代表在今年马拉松之后讲了一次团队的基本功训练。</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/Myhs654cf361ac6f?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/开源之夜/知识管理开源 小红书、医疗和个人-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>单元模型开源：轰趴、美业和SaaS</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>罗明铭</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/1Fsp6555f98003b7?tab=content</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/开源之夜/单元模型开源 轰趴、美业和SaaS-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>开源1：周子敬的以太大航海复盘</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>周子敬</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/6Wb6653104d621e6?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/开源之夜/开源1 周子敬的以太大航海复盘-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>落地大课：我用一堂开出千家棋牌室</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>杜金科</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/4lP16721e8464f13?tab=content</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/落地之夜/落地大课 我用一堂开出千家棋牌室-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>落地3：乡村、驾照科一和轰趴</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>班铭阳</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/F5NZ66ab1d6f9c3c?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/落地之夜/落地3 乡村、驾照科一和轰趴-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>落地5：门窗业务、加油站和驾校</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>蔡文超</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/2nNY6926c0ef3fe5?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/落地之夜/落地5 门窗业务、加油站和驾校-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>落地2：棋牌室、秋月梨和停车库</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>杜金科</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/OVrp64ba04af8177?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/落地之夜/落地2 棋牌室、秋月梨和停车库-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>落地4：小皇鸡、医院和咖啡含片</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>覃嘉璐</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/PBPz6787788f8628?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/落地之夜/落地4 小皇鸡、医院和咖啡含片-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>如何把萝卜干单品从0卖爆1个亿</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>何发</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/eB5g6629d69360b0?tab=content</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/科学体系/如何把萝卜干单品从0卖爆1个亿-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>觉醒之旅：大表哥的低成本创业</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>刘涛</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://yitang.top/redirect?justPay=1&amp;redirect=/lesson/IPZs647037426be4</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/科学体系/觉醒之旅 大表哥的低成本创业-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>从新人入局到十年百家奶茶店</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>古董</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/RZ_W64a68574e0e0?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/科学体系/从新人入局到十年百家奶茶店-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>加速成长：4个最佳实践学习案例</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>毕然</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/5Q2a65e02e3dd300?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/基本功高手/加速成长 4个最佳实践学习案例-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>决策案例：从艰难选择到科学笃定</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>陈建弛</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/SUUz648ac61e1cb9?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/决策高手/决策案例 从艰难选择到科学笃定-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>决策案例：古董十年百店大复盘</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>董晓峰</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/GhaD658323f60763?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/决策高手/决策案例 古董十年百店大复盘-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr"/>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>解决方案：3个产品内核迭代案例</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>何发</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/97gA66063a6264d6?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/内核高手/解决方案 3个产品内核迭代案例-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr"/>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>搞砸3：团购、品牌和新能源</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>杨晓光</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/WWqT64cb5fcdc131?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/搞砸之夜/搞砸3 团购、品牌和新能源-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr"/>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>搞砸7：智能硬件、密室和综测平台</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>李囧囧</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/ShfO67ffb3bb2546?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/搞砸之夜/搞砸7 智能硬件、密室和综测平台-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr"/>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>搞砸6：美妆体验空间和鸭货店</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>潘蕾蕾</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/NKsi67106014170a?_uds=homepage</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/搞砸之夜/搞砸6 美妆体验空间和鸭货店-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr"/>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>搞砸2：监控、校车和APP</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>赵耀军</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/nAXj6442060d5491?_uds=null</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/搞砸之夜/搞砸2 监控、校车和APP-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr"/>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>搞砸4：医美、沃柑和袋泡茶</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>金宝珠</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/BwH06657e6b382e1?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/搞砸之夜/搞砸4 医美、沃柑和袋泡茶-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr"/>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>搞砸5：铜锅牛肉、柠檬茶和炸鸡</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>仲洋</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/NRks66908c966957?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr"/>
+      <c r="X91" t="inlineStr"/>
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/案例必修/搞砸之夜/搞砸5 铜锅牛肉、柠檬茶和炸鸡-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr"/>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>会员必读：一堂新手指南（免券）</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/ImSz6086b0fb3d55?tab=content</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr"/>
+      <c r="X92" t="inlineStr"/>
+      <c r="Y92" t="inlineStr"/>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/其他课程/未分类/会员必读 一堂新手指南(免券)-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr"/>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>会员入学</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/luvS64ef293fbe0d?_uds=caidan_fwh_yitang</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr"/>
+      <c r="X93" t="inlineStr"/>
+      <c r="Y93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/其他课程/未分类/会员入学 第一课 (免券必学)-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr"/>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>图片数: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>5月会员日</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="inlineStr"/>
+      <c r="X94" t="inlineStr"/>
+      <c r="Y94" t="inlineStr"/>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/商业大航海/5月会员日-Truman/5月会员日-Truman-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr"/>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>半肥猫</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr"/>
+      <c r="X95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr"/>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/商业大航海/半肥猫-把课程变成AI工具和Skill/半肥猫-把课程变成AI工具和Skill-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr"/>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>专家分享｜如何用业务公式，驱动业务不断提升？（孔源）</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>孔源（一堂创始合伙人）</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="inlineStr"/>
+      <c r="X96" t="inlineStr"/>
+      <c r="Y96" t="inlineStr"/>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/商业大航海/如何用业务公式驱动业务不断提升/如何用业务公式驱动业务不断提升-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr"/>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>图片数: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>马易</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="inlineStr"/>
+      <c r="X97" t="inlineStr"/>
+      <c r="Y97" t="inlineStr"/>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/商业大航海/马易AMA精华笔记/马易AMA精华笔记-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr"/>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>张磊</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr"/>
+      <c r="X98" t="inlineStr"/>
+      <c r="Y98" t="inlineStr"/>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/商业大航海/张磊-精益测试AMA/张磊-精益测试AMA-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr"/>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>花总</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/商业大航海/花总AMA精华笔记/花总AMA精华笔记-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>于陆</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/商业大航海/于陆-AI工具与工作流AMA/于陆-AI工具与工作流AMA-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr"/>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>ROI实操4：落地训练篇</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/hNla692feb37d7ac?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="inlineStr"/>
+      <c r="Y101" t="inlineStr"/>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/做决策/ROI实操4 落地训练篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr"/>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>一堂创业课</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="inlineStr"/>
+      <c r="X102" t="inlineStr"/>
+      <c r="Y102" t="inlineStr"/>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/做决策/ROI实操3：提升高度篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr"/>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>图片数: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>全员必修：科学决策审美篇</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/RlY0641830d438b3?tab=content</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="inlineStr"/>
+      <c r="X103" t="inlineStr"/>
+      <c r="Y103" t="inlineStr"/>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/做决策/全员必修 科学决策审美篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr"/>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>图片数: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ROI实操1：提升宽度篇</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/bRf_642e65080607?tab=content</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="inlineStr"/>
+      <c r="X104" t="inlineStr"/>
+      <c r="Y104" t="inlineStr"/>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/做决策/ROI实操1 提升宽度篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr"/>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ROI实操2：提升深度篇</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>你这个事情不适合融资啊，投资人不看的，你知道能做大上市的Benchmark是多少么？</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/DkmC645db1662eb9?_uds=null&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
+      <c r="W105" t="inlineStr"/>
+      <c r="X105" t="inlineStr"/>
+      <c r="Y105" t="inlineStr"/>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/做决策/ROI实操2 提升深度篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr"/>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>重新理解「合伙股权」</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>芦玮娜</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/hOM45f3f9599823d?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="inlineStr"/>
+      <c r="Y106" t="inlineStr"/>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/分股权/重新理解「合伙股权」-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr"/>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>全员必修：业务公式导入篇</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/v0A0661280270ac7?_uds=fwh_lesson_map&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="inlineStr"/>
+      <c r="X107" t="inlineStr"/>
+      <c r="Y107" t="inlineStr"/>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/提业务/全员必修 业务公式导入篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr"/>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>业务公式实操1：建立公式篇</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/2Zvx67bee8335b11?tab=content</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
+      <c r="W108" t="inlineStr"/>
+      <c r="X108" t="inlineStr"/>
+      <c r="Y108" t="inlineStr"/>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/提业务/业务公式实操1 建立公式篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr"/>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>业务公式实操3：逻辑关系篇</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/0dG1686e1e170555?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
+      <c r="X109" t="inlineStr"/>
+      <c r="Y109" t="inlineStr"/>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/提业务/业务公式实操3 逻辑关系篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr"/>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>业务公式实操2：参数探索篇</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/t_24681afca7b7c3?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
+      <c r="X110" t="inlineStr"/>
+      <c r="Y110" t="inlineStr"/>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/提业务/业务公式实操2 参数探索篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr"/>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>业务公式实操4：假设落地篇</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/LOrJ691d97fc48e1?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
+      <c r="X111" t="inlineStr"/>
+      <c r="Y111" t="inlineStr"/>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/提业务/业务公式实操4 假设落地篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr"/>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>新人落地：新人Landing必修课</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>春萍</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/VguJ6408361e597c?tab=content</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
+      <c r="W112" t="inlineStr"/>
+      <c r="X112" t="inlineStr"/>
+      <c r="Y112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/会落地/新人落地 新人Landing必修课-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr"/>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>场景篇：基本功落地场景</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>春萍</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/Bkuy6901b79e26a7?_uds=latest-courses&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
+      <c r="W113" t="inlineStr"/>
+      <c r="X113" t="inlineStr"/>
+      <c r="Y113" t="inlineStr"/>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/基本功/场景篇 基本功落地场景-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr"/>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>基本功实操2：基本功落地武器库</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/9l2x672055addc5e?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="inlineStr"/>
+      <c r="X114" t="inlineStr"/>
+      <c r="Y114" t="inlineStr"/>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/基本功/基本功实操2 基本功落地武器库-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr"/>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>基本功实操1：关键基本功拆解</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/W0vc67105f3fa2fe?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
+      <c r="W115" t="inlineStr"/>
+      <c r="X115" t="inlineStr"/>
+      <c r="Y115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/基本功/基本功实操1 关键基本功拆解-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr"/>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>全员必修：重新理解苦练基本功</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/PgFs66986874790f?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
+      <c r="W116" t="inlineStr"/>
+      <c r="X116" t="inlineStr"/>
+      <c r="Y116" t="inlineStr"/>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/基本功/全员必修 重新理解苦练基本功-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr"/>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>知识库：团队知识管理必修课</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/QjU_64c77aa6dbbf?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
+      <c r="W117" t="inlineStr"/>
+      <c r="X117" t="inlineStr"/>
+      <c r="Y117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/做沉淀/知识库 团队知识管理必修课-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr"/>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>武器库：科学开会实操篇</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>春萍</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/tsZ164379403099d?_uds=null&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr"/>
+      <c r="X118" t="inlineStr"/>
+      <c r="Y118" t="inlineStr"/>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/会开会/武器库 科学开会实操篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr"/>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>图片数: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>认知篇：科学开会必修课</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>春萍</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/HUCz642553a2b2c1?tab=content</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
+      <c r="W119" t="inlineStr"/>
+      <c r="X119" t="inlineStr"/>
+      <c r="Y119" t="inlineStr"/>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/会开会/认知篇 科学开会必修课-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr"/>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>一堂创业课</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
+      <c r="W120" t="inlineStr"/>
+      <c r="X120" t="inlineStr"/>
+      <c r="Y120" t="inlineStr"/>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/专项课：产品经理招聘必修课/专项课：产品经理招聘必修课-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr"/>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>图片数: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>转化率黑客4：触点实操篇</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/fgXa66a9dee24480?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr"/>
+      <c r="X121" t="inlineStr"/>
+      <c r="Y121" t="inlineStr"/>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/提转化/转化率黑客4 触点实操篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr"/>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>转化率黑客5：组合落地篇</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/d2iQ6760ec1bc241?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
+      <c r="W122" t="inlineStr"/>
+      <c r="X122" t="inlineStr"/>
+      <c r="Y122" t="inlineStr"/>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/提转化/转化率黑客5 组合落地篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr"/>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>转化率黑客2：动力实操篇</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/j31766694eaebb1d?_uds=fwh_lesson_map&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
+      <c r="W123" t="inlineStr"/>
+      <c r="X123" t="inlineStr"/>
+      <c r="Y123" t="inlineStr"/>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/提转化/转化率黑客2 动力实操篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr"/>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>全员必修：转化率黑客认知篇</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/544s663b4f594151?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
+      <c r="W124" t="inlineStr"/>
+      <c r="X124" t="inlineStr"/>
+      <c r="Y124" t="inlineStr"/>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/提转化/全员必修 转化率黑客认知篇 (转化率黑客1)-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr"/>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>转化率黑客3：阻力实操篇</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Truman</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/k8RN66a0563fc9d5?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
+      <c r="W125" t="inlineStr"/>
+      <c r="X125" t="inlineStr"/>
+      <c r="Y125" t="inlineStr"/>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/提转化/转化率黑客3 阻力实操篇-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr"/>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>一堂创业课</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr"/>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
+      <c r="W126" t="inlineStr"/>
+      <c r="X126" t="inlineStr"/>
+      <c r="Y126" t="inlineStr"/>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/工具篇：用OKR挑战高难的目标/工具篇：用OKR挑战高难的目标-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr"/>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>图片数: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>经营必修：重新理解「战略会」</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>劉䘙</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://yitang.top/lesson/8xgW658a687195d8?_uds=homepage&amp;tab=content</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr"/>
+      <c r="W127" t="inlineStr"/>
+      <c r="X127" t="inlineStr"/>
+      <c r="Y127" t="inlineStr"/>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>本地已有</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>/Users/apple/Documents/mycc/2-Projects/P003-YITANG-Study/004-正式课程/管理必修/做战略/经营必修 重新理解「战略会」-文稿.md</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr"/>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>图片数: 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
